--- a/outputs/53167.xlsx
+++ b/outputs/53167.xlsx
@@ -146,23 +146,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -422,7 +422,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.83"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -436,7 +436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -447,11 +447,11 @@
         <v>120</v>
       </c>
       <c r="E4" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B4,B4)=1,0,LOOKUP(2,1/($B$4:B3=B4),$D$4:D3)-D4)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B3=B4),$D$3:D3)-D4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -462,11 +462,11 @@
         <v>120</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B5,B5)=1,0,LOOKUP(2,1/($B$4:B4=B5),$D$4:D4)-D5)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B4=B5),$D$3:D4)-D5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
@@ -477,11 +477,11 @@
         <v>110</v>
       </c>
       <c r="E6" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B6,B6)=1,0,LOOKUP(2,1/($B$4:B5=B6),$D$4:D5)-D6)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B5=B6),$D$3:D5)-D6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -492,11 +492,11 @@
         <v>105</v>
       </c>
       <c r="E7" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B7,B7)=1,0,LOOKUP(2,1/($B$4:B6=B7),$D$4:D6)-D7)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B6=B7),$D$3:D6)-D7,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
@@ -507,11 +507,11 @@
         <v>100</v>
       </c>
       <c r="E8" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B8,B8)=1,0,LOOKUP(2,1/($B$4:B7=B8),$D$4:D7)-D8)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B7=B8),$D$3:D7)-D8,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
@@ -522,11 +522,11 @@
         <v>110</v>
       </c>
       <c r="E9" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B9,B9)=1,0,LOOKUP(2,1/($B$4:B8=B9),$D$4:D8)-D9)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B8=B9),$D$3:D8)-D9,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
@@ -537,11 +537,11 @@
         <v>120</v>
       </c>
       <c r="E10" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B10,B10)=1,0,LOOKUP(2,1/($B$4:B9=B10),$D$4:D9)-D10)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B9=B10),$D$3:D9)-D10,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
@@ -552,11 +552,11 @@
         <v>115</v>
       </c>
       <c r="E11" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B11,B11)=1,0,LOOKUP(2,1/($B$4:B10=B11),$D$4:D10)-D11)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B10=B11),$D$3:D10)-D11,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
@@ -567,11 +567,11 @@
         <v>102</v>
       </c>
       <c r="E12" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B12,B12)=1,0,LOOKUP(2,1/($B$4:B11=B12),$D$4:D11)-D12)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B11=B12),$D$3:D11)-D12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
@@ -582,11 +582,11 @@
         <v>101</v>
       </c>
       <c r="E13" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B13,B13)=1,0,LOOKUP(2,1/($B$4:B12=B13),$D$4:D12)-D13)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B12=B13),$D$3:D12)-D13,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
         <v>4</v>
       </c>
@@ -597,11 +597,11 @@
         <v>95</v>
       </c>
       <c r="E14" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B14,B14)=1,0,LOOKUP(2,1/($B$4:B13=B14),$D$4:D13)-D14)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B13=B14),$D$3:D13)-D14,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
@@ -612,11 +612,11 @@
         <v>120</v>
       </c>
       <c r="E15" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B15,B15)=1,0,LOOKUP(2,1/($B$4:B14=B15),$D$4:D14)-D15)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B14=B15),$D$3:D14)-D15,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
@@ -627,7 +627,7 @@
         <v>100</v>
       </c>
       <c r="E16" s="5" t="n">
-        <f aca="false">IF(COUNTIF($B$4:B16,B16)=1,0,LOOKUP(2,1/($B$4:B15=B16),$D$4:D15)-D16)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B15=B16),$D$3:D15)-D16,0)</f>
         <v>20</v>
       </c>
     </row>

--- a/outputs/53167.xlsx
+++ b/outputs/53167.xlsx
@@ -422,7 +422,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.83"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -436,7 +436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
@@ -447,11 +447,10 @@
         <v>120</v>
       </c>
       <c r="E4" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B3=B4),$D$3:D3)-D4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
@@ -462,11 +461,10 @@
         <v>120</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B4=B5),$D$3:D4)-D5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
@@ -477,11 +475,10 @@
         <v>110</v>
       </c>
       <c r="E6" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B5=B6),$D$3:D5)-D6,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -492,11 +489,10 @@
         <v>105</v>
       </c>
       <c r="E7" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B6=B7),$D$3:D6)-D7,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
@@ -507,11 +503,10 @@
         <v>100</v>
       </c>
       <c r="E8" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B7=B8),$D$3:D7)-D8,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
@@ -522,11 +517,10 @@
         <v>110</v>
       </c>
       <c r="E9" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B8=B9),$D$3:D8)-D9,0)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
@@ -537,11 +531,10 @@
         <v>120</v>
       </c>
       <c r="E10" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B9=B10),$D$3:D9)-D10,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
@@ -552,11 +545,10 @@
         <v>115</v>
       </c>
       <c r="E11" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B10=B11),$D$3:D10)-D11,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
@@ -567,11 +559,10 @@
         <v>102</v>
       </c>
       <c r="E12" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B11=B12),$D$3:D11)-D12,0)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
@@ -582,11 +573,10 @@
         <v>101</v>
       </c>
       <c r="E13" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B12=B13),$D$3:D12)-D13,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
         <v>4</v>
       </c>
@@ -597,11 +587,10 @@
         <v>95</v>
       </c>
       <c r="E14" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B13=B14),$D$3:D13)-D14,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
@@ -612,11 +601,10 @@
         <v>120</v>
       </c>
       <c r="E15" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B14=B15),$D$3:D14)-D15,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
@@ -627,7 +615,6 @@
         <v>100</v>
       </c>
       <c r="E16" s="5" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/($B$3:B15=B16),$D$3:D15)-D16,0)</f>
         <v>20</v>
       </c>
     </row>
